--- a/J30/Output_files/MHE_Journal_Outbound_results.xlsx
+++ b/J30/Output_files/MHE_Journal_Outbound_results.xlsx
@@ -498,17 +498,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DEI-2026-01-28-05-00-27-584-5jz6</t>
+          <t>DEI-2026-03-05-21-35-57-852-mHl6</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00081012220267077804</t>
+          <t>20260130075153000027</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PPK_DEI_TaskRelease</t>
+          <t>RetrievalTaskResult</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -521,12 +521,12 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>system-msg-user@1081</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-01-28T05:01:10.001132</t>
+          <t>2026-03-05T21:36:43.188551</t>
         </is>
       </c>
     </row>
@@ -543,17 +543,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEI-2026-01-28-05-06-22-231-5JcY</t>
+          <t>DEI-2026-03-05-21-35-59-380-B9eE</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00081012220267077804</t>
+          <t>20260130075153000027</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PackTaskResult</t>
+          <t>PTW_DEI_AllocationCreated</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -561,16 +561,8 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>DATA_ERROR</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Task maintenance by WCS</t>
-        </is>
-      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
@@ -579,7 +571,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-01-28T05:06:50.033709</t>
+          <t>2026-03-05T21:36:43.191526</t>
         </is>
       </c>
     </row>
@@ -596,17 +588,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEI-2026-01-28-05-06-13-258-SLD0</t>
+          <t>DEI-2026-03-05-21-36-10-458-xQb9</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00081012220267077804</t>
+          <t>20260202093307000077</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>PPK_DEI_PickingFeedback</t>
+          <t>RetrievalTaskResult</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -624,7 +616,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-01-28T05:06:50.033749</t>
+          <t>2026-03-05T21:36:43.190020</t>
         </is>
       </c>
     </row>
@@ -641,17 +633,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEI-2026-01-28-05-06-09-946-0SJF</t>
+          <t>DEI-2026-03-05-21-36-11-377-jpCU</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00081012220267077804</t>
+          <t>20260202093307000077</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RetrievalTaskResult</t>
+          <t>PTW_DEI_AllocationCreated</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -669,7 +661,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-01-28T05:06:50.033839</t>
+          <t>2026-03-05T21:36:43.190973</t>
         </is>
       </c>
     </row>
@@ -686,17 +678,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DEI-2026-01-28-05-07-55-840-PTev</t>
+          <t>DEI-2026-03-05-11-06-55-513-7VeY</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>00081012220267077804</t>
+          <t>20260202093307000096</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>GoodsholderDivertedDueToException</t>
+          <t>RetrievalTaskResult</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -714,7 +706,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-01-28T05:08:40.029280</t>
+          <t>2026-03-05T11:07:38.283938</t>
         </is>
       </c>
     </row>

--- a/J30/Output_files/MHE_Journal_Outbound_results.xlsx
+++ b/J30/Output_files/MHE_Journal_Outbound_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,17 +498,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DEI-2026-03-05-21-35-57-852-mHl6</t>
+          <t>DEI-2026-03-19-09-36-38-674-H9dk</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>20260130075153000027</t>
+          <t>20260317163508000009</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RetrievalTaskResult</t>
+          <t>PTW_DEI_AllocationCreated</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -526,7 +526,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-03-05T21:36:43.188551</t>
+          <t>2026-03-19T09:37:05.743958</t>
         </is>
       </c>
     </row>
@@ -543,12 +543,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEI-2026-03-05-21-35-59-380-B9eE</t>
+          <t>DEI-2026-03-19-09-36-38-674-H9dk</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20260130075153000027</t>
+          <t>20260317163508000009</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-03-05T21:36:43.191526</t>
+          <t>2026-03-19T09:37:05.743958</t>
         </is>
       </c>
     </row>
@@ -588,17 +588,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEI-2026-03-05-21-36-10-458-xQb9</t>
+          <t>DEI-2026-03-23-02-00-24-498-7fQS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>20260202093307000077</t>
+          <t>20260317163508000009</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RetrievalTaskResult</t>
+          <t>PPK_DEI_TaskRelease</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -611,12 +611,12 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>system-msg-user@1081</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-03-05T21:36:43.190020</t>
+          <t>2026-03-23T02:01:05.954894</t>
         </is>
       </c>
     </row>
@@ -633,17 +633,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEI-2026-03-05-21-36-11-377-jpCU</t>
+          <t>DEI-2026-03-23-02-00-24-498-7fQS</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>20260202093307000077</t>
+          <t>20260317163508000009</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PTW_DEI_AllocationCreated</t>
+          <t>PPK_DEI_TaskRelease</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -656,12 +656,12 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>system-msg-user@1081</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-03-05T21:36:43.190973</t>
+          <t>2026-03-23T02:01:05.954894</t>
         </is>
       </c>
     </row>
@@ -678,12 +678,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DEI-2026-03-05-11-06-55-513-7VeY</t>
+          <t>DEI-2026-03-23-02-01-10-458-tZGc</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>20260202093307000096</t>
+          <t>20260317163508000009</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -706,7 +706,142 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-03-05T11:07:38.283938</t>
+          <t>2026-03-23T02:01:55.961938</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-23-02-01-10-458-tZGc</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>20260317163508000009</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RetrievalTaskResult</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-03-23T02:01:55.961938</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-23-02-01-18-498-Mjgj</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>20260317163508000009</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-03-23T02:01:55.963029</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-23-02-01-18-498-Mjgj</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>20260317163508000009</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-03-23T02:01:55.963029</t>
         </is>
       </c>
     </row>

--- a/J30/Output_files/MHE_Journal_Outbound_results.xlsx
+++ b/J30/Output_files/MHE_Journal_Outbound_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,35 +451,25 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Spur_ID</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Message_Type</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>ReasonCode</t>
-        </is>
-      </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>VendorCodeDesc</t>
+          <t>User</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>DivertedLocation</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>User</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Created_on</t>
         </is>
@@ -498,35 +488,33 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DEI-2026-03-19-09-36-38-674-H9dk</t>
+          <t>DEI-2026-04-01-14-05-53-538-X5mf</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>20260317163508000009</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>PTW_DEI_AllocationCreated</t>
-        </is>
-      </c>
+          <t>00008884070000015342</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
+          <t>Pack_Complete</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>nike-nas-user</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2026-03-19T09:37:05.743958</t>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-04-01T14:06:34.421387</t>
         </is>
       </c>
     </row>
@@ -543,35 +531,33 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEI-2026-03-19-09-36-38-674-H9dk</t>
+          <t>DEI-2026-04-01-14-08-04-657-rOgd</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20260317163508000009</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>PTW_DEI_AllocationCreated</t>
-        </is>
-      </c>
+          <t>00008884070000015342</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>nike-nas-user</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2026-03-19T09:37:05.743958</t>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-04-01T14:08:54.419942</t>
         </is>
       </c>
     </row>
@@ -588,260 +574,37 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEI-2026-03-23-02-00-24-498-7fQS</t>
+          <t>DEI-2026-04-01-14-08-15-502-9ylt</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>20260317163508000009</t>
+          <t>00008884070000015342</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>PPK_DEI_TaskRelease</t>
+          <t>6205000000</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>RoutingTaskResult</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>system-msg-user@1081</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2026-03-23T02:01:05.954894</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>DEI-2026-03-23-02-00-24-498-7fQS</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>20260317163508000009</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>PPK_DEI_TaskRelease</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>system-msg-user@1081</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2026-03-23T02:01:05.954894</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>DEI-2026-03-23-02-01-10-458-tZGc</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>20260317163508000009</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>RetrievalTaskResult</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>nike-nas-user</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2026-03-23T02:01:55.961938</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>DEI-2026-03-23-02-01-10-458-tZGc</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>20260317163508000009</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>RetrievalTaskResult</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>nike-nas-user</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2026-03-23T02:01:55.961938</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>DEI-2026-03-23-02-01-18-498-Mjgj</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>20260317163508000009</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>PTW_DEI_AllocationCreated</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>nike-nas-user</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2026-03-23T02:01:55.963029</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>DEI-2026-03-23-02-01-18-498-Mjgj</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>20260317163508000009</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>PTW_DEI_AllocationCreated</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>nike-nas-user</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2026-03-23T02:01:55.963029</t>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-04-01T14:08:54.421159</t>
         </is>
       </c>
     </row>

--- a/J30/Output_files/MHE_Journal_Outbound_results.xlsx
+++ b/J30/Output_files/MHE_Journal_Outbound_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,18 +488,18 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DEI-2026-04-01-14-05-53-538-X5mf</t>
+          <t>DEI-2026-04-07-15-30-23-526-ERGY</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00008884070000015342</t>
+          <t>00008884070000016691</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pack_Complete</t>
+          <t>PPK_DEI_TaskRelease</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -509,12 +509,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>vgana3</t>
+          <t>system-msg-user@1081</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-04-01T14:06:34.421387</t>
+          <t>2026-04-07T15:31:04.783688</t>
         </is>
       </c>
     </row>
@@ -531,18 +531,18 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEI-2026-04-01-14-08-04-657-rOgd</t>
+          <t>DEI-2026-04-07-16-46-37-602-3vCI</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00008884070000015342</t>
+          <t>00008884070000016691</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>GoodsholderMeasured</t>
+          <t>PickTaskResult</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-04-01T14:08:54.419942</t>
+          <t>2026-04-07T16:47:24.569832</t>
         </is>
       </c>
     </row>
@@ -574,37 +574,123 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEI-2026-04-01-14-08-15-502-9ylt</t>
+          <t>DEI-2026-04-07-16-50-06-853-n44Z</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00008884070000015342</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+          <t>00008884070000016691</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Pack_Complete</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-04-07T16:50:54.584597</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>DEI-2026-04-07-16-52-45-729-fJp1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>00008884070000016691</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-04-07T16:53:34.596760</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DEI-2026-04-07-16-52-55-356-bHJQ</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>00008884070000016691</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>6205000000</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>RoutingTaskResult</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>nike-nas-user</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2026-04-01T14:08:54.421159</t>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-04-07T16:53:34.596760</t>
         </is>
       </c>
     </row>

--- a/J30/Output_files/MHE_Journal_Outbound_results.xlsx
+++ b/J30/Output_files/MHE_Journal_Outbound_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,12 +488,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DEI-2026-04-07-15-30-23-526-ERGY</t>
+          <t>DEI-2026-04-08-23-40-22-491-R9Bh</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00008884070000016691</t>
+          <t>00008884070000017223</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -514,7 +514,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-04-07T15:31:04.783688</t>
+          <t>2026-04-08T23:41:03.468346</t>
         </is>
       </c>
     </row>
@@ -531,18 +531,18 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEI-2026-04-07-16-46-37-602-3vCI</t>
+          <t>DEI-2026-04-08-23-43-46-724-hw59</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00008884070000016691</t>
+          <t>00008884070000017223</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PickTaskResult</t>
+          <t>Pack_Complete</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-04-07T16:47:24.569832</t>
+          <t>2026-04-08T23:44:33.488861</t>
         </is>
       </c>
     </row>
@@ -574,18 +574,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEI-2026-04-07-16-50-06-853-n44Z</t>
+          <t>DEI-2026-04-08-23-45-25-786-r2Hx</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00008884070000016691</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>00008884070000017223</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>6405000000</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pack_Complete</t>
+          <t>RoutingTaskResult</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -595,12 +599,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>vgana3</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-04-07T16:50:54.584597</t>
+          <t>2026-04-08T23:45:53.518040</t>
         </is>
       </c>
     </row>
@@ -617,12 +621,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEI-2026-04-07-16-52-45-729-fJp1</t>
+          <t>DEI-2026-04-08-23-45-14-801-udoS</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00008884070000016691</t>
+          <t>00008884070000017223</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -638,59 +642,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>system-msg-user@1081</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-04-07T16:53:34.596760</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>DEI-2026-04-07-16-52-55-356-bHJQ</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>00008884070000016691</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>6205000000</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>RoutingTaskResult</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>nike-nas-user</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-04-07T16:53:34.596760</t>
+          <t>2026-04-08T23:45:53.518465</t>
         </is>
       </c>
     </row>

--- a/J30/Output_files/MHE_Journal_Outbound_results.xlsx
+++ b/J30/Output_files/MHE_Journal_Outbound_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,12 +488,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DEI-2026-04-08-23-40-22-491-R9Bh</t>
+          <t>DEI-2026-04-15-21-40-34-116-ptwy-SPLIT-7</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00008884070000017223</t>
+          <t>00008884070000200687</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -514,7 +514,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-04-08T23:41:03.468346</t>
+          <t>2026-04-15T21:41:15.374725</t>
         </is>
       </c>
     </row>
@@ -531,18 +531,18 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEI-2026-04-08-23-43-46-724-hw59</t>
+          <t>DEI-2026-04-15-21-40-34-116-ptwy-SPLIT-8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00008884070000017223</t>
+          <t>00008884070000200694</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pack_Complete</t>
+          <t>PPK_DEI_TaskRelease</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>system-msg-user@1081</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-04-08T23:44:33.488861</t>
+          <t>2026-04-15T21:41:15.374725</t>
         </is>
       </c>
     </row>
@@ -574,22 +574,18 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEI-2026-04-08-23-45-25-786-r2Hx</t>
+          <t>DEI-2026-04-15-21-40-34-116-ptwy-SPLIT-2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00008884070000017223</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>6405000000</t>
-        </is>
-      </c>
+          <t>00008884070000200700</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>RoutingTaskResult</t>
+          <t>PPK_DEI_TaskRelease</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -599,12 +595,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>system-msg-user@1081</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-04-08T23:45:53.518040</t>
+          <t>2026-04-15T21:41:15.382234</t>
         </is>
       </c>
     </row>
@@ -621,18 +617,18 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEI-2026-04-08-23-45-14-801-udoS</t>
+          <t>DEI-2026-04-15-21-40-34-116-ptwy-SPLIT-4</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00008884070000017223</t>
+          <t>00008884070000200717</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>GoodsholderMeasured</t>
+          <t>PPK_DEI_TaskRelease</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -647,7 +643,222 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-04-08T23:45:53.518465</t>
+          <t>2026-04-15T21:41:15.382234</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DEI-2026-04-15-21-40-34-116-ptwy-SPLIT-3</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>00008884070000200724</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>PPK_DEI_TaskRelease</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>system-msg-user@1081</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-04-15T21:41:15.382234</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DEI-2026-04-15-21-40-34-116-ptwy-SPLIT-5</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>00008884070000200731</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>PPK_DEI_TaskRelease</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>system-msg-user@1081</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-04-15T21:41:15.374725</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DEI-2026-04-15-21-40-34-116-ptwy-SPLIT-9</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>00008884070000200748</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>PPK_DEI_TaskRelease</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>system-msg-user@1081</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-04-15T21:41:15.376567</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>DEI-2026-04-15-21-40-34-116-ptwy-SPLIT-6</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>00008884070000200755</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>PPK_DEI_TaskRelease</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>system-msg-user@1081</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-04-15T21:41:15.375646</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>DEI-2026-04-15-21-40-34-116-ptwy-SPLIT-1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>00008884070000200762</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>PPK_DEI_TaskRelease</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>system-msg-user@1081</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-04-15T21:41:15.382234</t>
         </is>
       </c>
     </row>
